--- a/artfynd/A 69154-2021 artfynd.xlsx
+++ b/artfynd/A 69154-2021 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>134589661</v>
       </c>
       <c r="B4" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>134589680</v>
       </c>
       <c r="B5" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>134589713</v>
       </c>
       <c r="B6" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 69154-2021 artfynd.xlsx
+++ b/artfynd/A 69154-2021 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>134589661</v>
       </c>
       <c r="B4" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>134589680</v>
       </c>
       <c r="B5" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>134589713</v>
       </c>
       <c r="B6" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 69154-2021 artfynd.xlsx
+++ b/artfynd/A 69154-2021 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>134589661</v>
       </c>
       <c r="B4" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>134589680</v>
       </c>
       <c r="B5" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>134589713</v>
       </c>
       <c r="B6" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 69154-2021 artfynd.xlsx
+++ b/artfynd/A 69154-2021 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>134589661</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>134589680</v>
       </c>
       <c r="B5" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>134589713</v>
       </c>
       <c r="B6" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
